--- a/Contenu_MAJ_Entete/ig/all-profiles.xlsx
+++ b/Contenu_MAJ_Entete/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T09:02:13+00:00</t>
+    <t>2024-06-06T14:52:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Contenu_MAJ_Entete/ig/all-profiles.xlsx
+++ b/Contenu_MAJ_Entete/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T14:52:04+00:00</t>
+    <t>2024-06-06T15:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Contenu_MAJ_Entete/ig/all-profiles.xlsx
+++ b/Contenu_MAJ_Entete/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T15:25:12+00:00</t>
+    <t>2024-06-06T15:40:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Contenu_MAJ_Entete/ig/all-profiles.xlsx
+++ b/Contenu_MAJ_Entete/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T15:40:05+00:00</t>
+    <t>2024-06-06T16:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Contenu_MAJ_Entete/ig/all-profiles.xlsx
+++ b/Contenu_MAJ_Entete/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T16:05:39+00:00</t>
+    <t>2024-06-06T16:48:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Contenu_MAJ_Entete/ig/all-profiles.xlsx
+++ b/Contenu_MAJ_Entete/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T16:48:29+00:00</t>
+    <t>2024-06-06T17:01:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
